--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportOrderTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportOrderTemplate.xlsx
@@ -31,6 +31,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -88,12 +91,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="37" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -379,20 +391,30 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.5703125" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="5" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Yêu cầu nhập dữ liệu kiểu số nguyên" sqref="B2:XFD1048576">
+      <formula1>0</formula1>
+      <formula2>10000000</formula2>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Yêu cầu nhập dữ liệu đúng định dạng MM/dd._x000a_Thời gian phải &gt;= 2024/01/01 và &lt;= 2100/12/31" sqref="B1:XFD1">
+      <formula1>45292</formula1>
+      <formula2>73415</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
